--- a/docs/My_Professional_Reviews/WOWUAS-5_score.xlsx
+++ b/docs/My_Professional_Reviews/WOWUAS-5_score.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felissha/Documents/GitHub/all/new-all-about-me/My_Professional_Reviews/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF8E0363-827F-5949-A812-A1919FD68447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{147AD401-D36D-D54B-8CB4-010CD392223A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{6449C1BB-AFE7-AE42-9DD7-1DEF8F5678D0}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="27080" windowHeight="16720" activeTab="3" xr2:uid="{6449C1BB-AFE7-AE42-9DD7-1DEF8F5678D0}"/>
   </bookViews>
   <sheets>
     <sheet name="UAS_1_My_Concepts" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="30">
   <si>
     <t>ID</t>
   </si>
@@ -118,7 +118,16 @@
     <t>UAS-4_Rata2</t>
   </si>
   <si>
-    <t>Felissha</t>
+    <t>Felissha Dunell Damanik</t>
+  </si>
+  <si>
+    <t>Hanan Fitra Salam</t>
+  </si>
+  <si>
+    <t>Muhammad Faris Daffa</t>
+  </si>
+  <si>
+    <t>Sherry Eunike</t>
   </si>
 </sst>
 </file>
@@ -609,9 +618,21 @@
       <c r="B3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="4" t="str">
+      <c r="C3" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2">
+        <v>5</v>
+      </c>
+      <c r="F3" s="2">
+        <v>5</v>
+      </c>
+      <c r="G3" s="4">
         <f t="shared" ref="G3:G66" si="0">IF(COUNT(C3:F3)=0,"",AVERAGE(C3:F3))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="L3" s="4"/>
       <c r="Q3" s="4"/>
@@ -622,9 +643,27 @@
       <c r="AP3" s="4"/>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="G4" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A4" s="2">
+        <v>18222133</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2">
+        <v>4</v>
+      </c>
+      <c r="D4" s="2">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2">
+        <v>4</v>
+      </c>
+      <c r="G4" s="4">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
       </c>
       <c r="L4" s="4"/>
       <c r="Q4" s="4"/>
@@ -635,9 +674,27 @@
       <c r="AP4" s="4"/>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="G5" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A5" s="2">
+        <v>18224025</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="D5" s="2">
+        <v>5</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2">
+        <v>4</v>
+      </c>
+      <c r="G5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.375</v>
       </c>
       <c r="L5" s="4"/>
       <c r="Q5" s="4"/>
@@ -648,9 +705,27 @@
       <c r="AP5" s="4"/>
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="G6" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A6" s="2">
+        <v>18224075</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="D6" s="2">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="G6" s="4">
+        <f t="shared" si="0"/>
+        <v>4.75</v>
       </c>
       <c r="L6" s="4"/>
       <c r="Q6" s="4"/>
@@ -1759,9 +1834,27 @@
       <c r="AP2" s="3"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="G3" s="4" t="str">
+      <c r="A3" s="2">
+        <v>18223099</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2">
+        <v>5</v>
+      </c>
+      <c r="F3" s="2">
+        <v>5</v>
+      </c>
+      <c r="G3" s="4">
         <f t="shared" ref="G3:G66" si="0">IF(COUNT(C3:F3)=0,"",AVERAGE(C3:F3))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="L3" s="4"/>
       <c r="Q3" s="4"/>
@@ -1772,9 +1865,27 @@
       <c r="AP3" s="4"/>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="G4" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A4" s="2">
+        <v>18222133</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2">
+        <v>4</v>
+      </c>
+      <c r="G4" s="4">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
       </c>
       <c r="L4" s="4"/>
       <c r="Q4" s="4"/>
@@ -1785,9 +1896,27 @@
       <c r="AP4" s="4"/>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="G5" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A5" s="2">
+        <v>18224025</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="2">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2">
+        <v>5</v>
+      </c>
+      <c r="E5" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="F5" s="2">
+        <v>4</v>
+      </c>
+      <c r="G5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.625</v>
       </c>
       <c r="L5" s="4"/>
       <c r="Q5" s="4"/>
@@ -1798,9 +1927,27 @@
       <c r="AP5" s="4"/>
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="G6" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A6" s="2">
+        <v>18224075</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="G6" s="4">
+        <f t="shared" si="0"/>
+        <v>4.875</v>
       </c>
       <c r="L6" s="4"/>
       <c r="Q6" s="4"/>
@@ -2909,9 +3056,27 @@
       <c r="AP2" s="3"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="G3" s="4" t="str">
+      <c r="A3" s="2">
+        <v>18223099</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2">
+        <v>5</v>
+      </c>
+      <c r="F3" s="2">
+        <v>5</v>
+      </c>
+      <c r="G3" s="4">
         <f t="shared" ref="G3:G66" si="0">IF(COUNT(C3:F3)=0,"",AVERAGE(C3:F3))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="L3" s="4"/>
       <c r="Q3" s="4"/>
@@ -2922,9 +3087,27 @@
       <c r="AP3" s="4"/>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="G4" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A4" s="2">
+        <v>18222133</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2">
+        <v>4</v>
+      </c>
+      <c r="E4" s="2">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2">
+        <v>5</v>
+      </c>
+      <c r="G4" s="4">
+        <f t="shared" si="0"/>
+        <v>4.75</v>
       </c>
       <c r="L4" s="4"/>
       <c r="Q4" s="4"/>
@@ -2935,9 +3118,26 @@
       <c r="AP4" s="4"/>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="G5" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A5" s="2">
+        <v>18224025</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="2">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2">
+        <v>5</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2">
+        <v>5</v>
+      </c>
+      <c r="G5" s="4">
+        <v>5</v>
       </c>
       <c r="L5" s="4"/>
       <c r="Q5" s="4"/>
@@ -2948,9 +3148,26 @@
       <c r="AP5" s="4"/>
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="G6" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A6" s="2">
+        <v>18224075</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2">
+        <v>5</v>
+      </c>
+      <c r="G6" s="4">
+        <v>5</v>
       </c>
       <c r="L6" s="4"/>
       <c r="Q6" s="4"/>
@@ -4059,9 +4276,27 @@
       <c r="AP2" s="3"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="G3" s="4" t="str">
+      <c r="A3" s="2">
+        <v>18223099</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2">
+        <v>5</v>
+      </c>
+      <c r="F3" s="2">
+        <v>5</v>
+      </c>
+      <c r="G3" s="4">
         <f t="shared" ref="G3:G66" si="0">IF(COUNT(C3:F3)=0,"",AVERAGE(C3:F3))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="L3" s="4"/>
       <c r="Q3" s="4"/>
@@ -4072,9 +4307,27 @@
       <c r="AP3" s="4"/>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="G4" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A4" s="2">
+        <v>18222133</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2">
+        <v>4</v>
+      </c>
+      <c r="D4" s="2">
+        <v>4</v>
+      </c>
+      <c r="E4" s="2">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2">
+        <v>4</v>
+      </c>
+      <c r="G4" s="4">
+        <f t="shared" si="0"/>
+        <v>4.25</v>
       </c>
       <c r="L4" s="4"/>
       <c r="Q4" s="4"/>
@@ -4085,9 +4338,27 @@
       <c r="AP4" s="4"/>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="G5" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A5" s="2">
+        <v>18224025</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="2">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="G5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.25</v>
       </c>
       <c r="L5" s="4"/>
       <c r="Q5" s="4"/>
@@ -4098,9 +4369,27 @@
       <c r="AP5" s="4"/>
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="G6" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A6" s="2">
+        <v>18224075</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="D6" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2">
+        <v>5</v>
+      </c>
+      <c r="G6" s="4">
+        <f t="shared" si="0"/>
+        <v>4.75</v>
       </c>
       <c r="L6" s="4"/>
       <c r="Q6" s="4"/>
